--- a/tams-svreport-batch/tams-svreport-batch-chb3/src/main/resources/tpl/EquityBusiInfoRegistCHB.xlsx
+++ b/tams-svreport-batch/tams-svreport-batch-chb3/src/main/resources/tpl/EquityBusiInfoRegistCHB.xlsx
@@ -5,14 +5,14 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\feature3.0.6\tams\tams-svreport-batch\tams-svreport-batch-chb3\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28700" windowHeight="12800"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="12795"/>
   </bookViews>
   <sheets>
-    <sheet name="业务明细信息登记" sheetId="1" r:id="rId1"/>
+    <sheet name="投资者明细信息登记" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
     <sheet name="版本号1.0.0" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -1705,22 +1705,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AA3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" style="28" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="22.625" style="28" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="18" style="28" customWidth="1" collapsed="1"/>
-    <col min="3" max="14" width="26.08203125" style="28" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="19.4140625" style="28" customWidth="1" collapsed="1"/>
-    <col min="17" max="18" width="26.08203125" style="28" customWidth="1" collapsed="1"/>
+    <col min="3" max="14" width="26.125" style="28" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="19.375" style="28" customWidth="1" collapsed="1"/>
+    <col min="17" max="18" width="26.125" style="28" customWidth="1" collapsed="1"/>
     <col min="19" max="19" width="18.5" style="28" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="26.08203125" style="28" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="18.4140625" style="28" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="19.4140625" style="28" customWidth="1" collapsed="1"/>
+    <col min="20" max="20" width="26.125" style="28" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" width="18.375" style="28" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="19.375" style="28" customWidth="1" collapsed="1"/>
     <col min="23" max="23" width="17.5" style="28" customWidth="1" collapsed="1"/>
     <col min="24" max="24" width="24" style="28" customWidth="1" collapsed="1"/>
     <col min="25" max="25" width="15.5" style="28" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="16.9140625" style="28" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="17.4140625" style="28" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="16.875" style="28" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="17.375" style="28" customWidth="1" collapsed="1"/>
     <col min="28" max="16384" width="9" style="29" collapsed="1"/>
   </cols>
   <sheetData>
@@ -1888,35 +1888,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A329"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="73.33203125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="73.375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5">
+    <row r="1" spans="1:1" ht="15.75">
       <c r="A1" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="31">
+    <row r="2" spans="1:1" ht="30">
       <c r="A2" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.5">
+    <row r="3" spans="1:1" ht="15.75">
       <c r="A3" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.5">
+    <row r="4" spans="1:1" ht="15.75">
       <c r="A4" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.5">
+    <row r="5" spans="1:1" ht="15.75">
       <c r="A5" s="10"/>
     </row>
-    <row r="6" spans="1:1" ht="15.5">
+    <row r="6" spans="1:1" ht="15.75">
       <c r="A6" s="11" t="s">
         <v>37</v>
       </c>
@@ -3541,9 +3541,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.58203125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="14.625" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="34" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
@@ -3563,7 +3563,7 @@
         <v>43761</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="29.15" customHeight="1">
+    <row r="3" spans="1:2" ht="29.1" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>321</v>
       </c>
